--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Kritina Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -869,10 +867,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -889,10 +885,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.64397</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.64397</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -944,25 +938,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33875</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33875</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,21 +483,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -517,10 +517,10 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -529,12 +529,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -978,6 +978,217 @@
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>no light on the STB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379169</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:29:57 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.669</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Sisha Cafe With Fast Food,Ekatamarga 34, ???????? , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>pragalrock@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>16:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L24-7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.34123</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 35m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -992,20 +1203,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1029,7 +1240,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1039,7 +1250,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1050,7 +1261,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1273,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1285,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
@@ -1115,14 +1326,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1173,14 +1384,14 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1256,6 +1467,73 @@
       <c r="M17" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379169</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:29:57 PM</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1048,10 +1048,8 @@
           <t>Pragal Kc</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9841915176</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9841915176</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1066,10 +1064,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9841915176</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9841915176</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1086,10 +1082,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.669</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.669</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1145,25 +1139,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L24-7</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.34123</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.34123</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1212,7 +1202,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1503,7 +1493,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1179,6 +1179,217 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgarde</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380004</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Chhechima Sherpa</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Chhechima Sherpa</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9818607638</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9818607638</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:33:24 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.730383</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Hamro Momo Ganatantra chowk, Boudha-6, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9826750385@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L55-4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.359308</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1202,7 +1413,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1230,7 +1441,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1240,7 +1451,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1251,7 +1462,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1486,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 20h 35m</t>
+          <t>1d 10h 18m</t>
         </is>
       </c>
     </row>
@@ -1312,218 +1523,326 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1379169</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Pragal Kc</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 01:29:57 PM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 20h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380004</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Chhechima Sherpa</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:33:24 AM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1249,10 +1249,8 @@
           <t>Chhechima Sherpa</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9818607638</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9818607638</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1267,10 +1265,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9818607638</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9818607638</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1287,10 +1283,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.730383</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.730383</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1346,50 +1340,149 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L55-4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.359308</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.359308</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1d 2m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1413,7 +1506,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1441,7 +1534,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1462,7 +1555,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1556,291 +1649,320 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TKT1379169</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Pragal Kc</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 01:29:57 PM</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>TKT1380004</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Chhechima Sherpa</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>27 Oct 2026 10:33:24 AM</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>1d 2m</t>
         </is>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1486,6 +1486,428 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379167</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9846802439</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9846802439</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:27:43 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.72929</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Near Tenzing ChowkKapan, Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>kamalnature772@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>17:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L50-4</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.360844</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 39m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wfi6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379187</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Dhijan Dahal</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Dhijan Dahal</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9862910031</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9862910031</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:44:30 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.734268</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Kapan Near  Trinetra Vidhya Niketan., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>dhijandahal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>17:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L4-2</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.353543</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1497,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1506,7 +1928,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1534,7 +1956,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1544,7 +1966,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1555,7 +1977,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1579,7 +2001,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 10h 18m</t>
+          <t>1d 15h 54m</t>
         </is>
       </c>
     </row>
@@ -1620,10 +2042,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1710,10 +2132,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1968,6 +2390,140 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379167</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:27:43 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379187</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Dhijan Dahal</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:44:30 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 21m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1543,20 +1543,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Kamal Pandit</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9846802439</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9846802439</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1571,10 +1565,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9846802439</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9846802439</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1591,10 +1583,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.72929</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.72929</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1650,25 +1640,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L50-4</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.360844</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.360844</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1754,20 +1740,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Dhijan Dahal</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9862910031</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9862910031</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1782,10 +1762,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9862910031</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9862910031</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1802,10 +1780,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.734268</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.734268</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1861,25 +1837,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L4-2</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.353543</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.353543</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wfi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -1928,7 +1900,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2423,7 +2395,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2490,7 +2462,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Case : wfi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -506,13 +506,13 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1880,6 +1880,213 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379325</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sanu Maya Tamang</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sanu Maya Tamang</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9849576316</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43:41 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>BKT9849576316</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:42:44 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43:41 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.69646053946493, 85.37977494133595, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9849576316@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>16:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L52-7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1891,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1900,7 +2107,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1928,7 +2135,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1938,7 +2145,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1949,7 +2156,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -1973,7 +2180,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 54m</t>
+          <t>1d 16h 43m</t>
         </is>
       </c>
     </row>
@@ -2032,14 +2239,14 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2139,181 +2346,137 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1379169</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Pragal Kc</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>IPTV STB Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 01:29:57 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1380004</t>
+          <t>TKT1379169</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Chhechima Sherpa</t>
+          <t>Pragal Kc</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2333,22 +2496,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>27 Oct 2026 10:33:24 AM</t>
+          <t>26 Oct 2026 01:29:57 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2358,19 +2521,19 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>1d 2m</t>
+          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1379167</t>
+          <t>TKT1380004</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Kamal Pandit</t>
+          <t>Chhechima Sherpa</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2400,22 +2563,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:27:43 PM</t>
+          <t>27 Oct 2026 10:33:24 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2425,74 +2588,208 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 39m</t>
+          <t>1d 2m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>TKT1379167</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:27:43 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>TKT1379187</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Dhijan Dahal</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Case : wfi6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 11:06:24 AM</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>26 Oct 2026 01:44:30 PM</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 11:06:24 AM</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t>1d 21h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379325</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Sanu Maya Tamang</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43:41 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:42:44 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43:41 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 20h</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1947,10 +1947,8 @@
           <t>Sanu Maya Tamang</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9849576316</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9849576316</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2022,10 +2020,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
@@ -2044,10 +2040,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2058,7 +2052,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2107,7 +2101,7 @@
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2759,7 +2753,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,12 +494,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2081,6 +2081,213 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>error 1400 issue in iptv</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379645</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>delight outsource security serves pvt</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>delight outsource security serves pvt</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9801887031</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18:27 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>BKT9801877031</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 07:31:56 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18:27 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>HALESI MART PVT. LTD - Convenience store Manohara park Madhyapur Thimi 44600, Bhaktapur, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9851236610@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>12:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L58-8</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 46m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2092,16 +2299,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2129,7 +2336,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2139,7 +2346,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2357,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2381,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 43m</t>
+          <t>1d 16h 44m</t>
         </is>
       </c>
     </row>
@@ -2245,97 +2452,92 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2347,264 +2549,176 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1379169</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Pragal Kc</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 01:29:57 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>1d 20h 35m</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1380004</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Chhechima Sherpa</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>27 Oct 2026 10:33:24 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 2m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1379167</t>
+          <t>TKT1379169</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Kamal Pandit</t>
+          <t>Pragal Kc</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2624,22 +2738,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:27:43 PM</t>
+          <t>26 Oct 2026 01:29:57 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2649,19 +2763,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 39m</t>
+          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1379187</t>
+          <t>TKT1380004</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Dhijan Dahal</t>
+          <t>Chhechima Sherpa</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2691,22 +2805,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wfi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:24 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:44:30 PM</t>
+          <t>27 Oct 2026 10:33:24 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:24 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2716,74 +2830,275 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 21m</t>
+          <t>1d 2m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>TKT1379167</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:27:43 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>1d 21h 39m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379187</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Dhijan Dahal</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:44:30 PM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>TKT1379325</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Sanu Maya Tamang</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 11:43:41 AM</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>26 Oct 2026 03:42:44 PM</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 11:43:41 AM</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>1d 20h</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379645</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>delight outsource security serves pvt</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18:27 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 07:31:56 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18:27 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 46m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2148,10 +2148,8 @@
           <t>delight outsource security serves pvt</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9801887031</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9801887031</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2223,10 +2221,8 @@
           <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2245,10 +2241,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2259,32 +2253,243 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 46m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379467</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Karanjit</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Karanjit</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841348904</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43:39 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9860976151</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43:39 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.68287</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near The Burger house and crunchy fried chicken (Gatthaghar), Madhyapur Thimi , Bagmati, Central, Ne</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>karanjitmanoj@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>15:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.3856</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>1d 16h 46m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 41m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2336,7 +2541,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2346,7 +2551,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2357,7 +2562,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2586,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 44m</t>
+          <t>1d 17h 9m</t>
         </is>
       </c>
     </row>
@@ -2422,10 +2627,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2530,10 +2735,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3068,14 +3273,14 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
           <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
           <t>28 Oct 2026 12:18:27 PM</t>
@@ -3099,6 +3304,73 @@
       <c r="M30" s="3" t="inlineStr">
         <is>
           <t>1d 16h 46m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379467</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Manoj Karanjit</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43:39 PM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43:39 PM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>1d 19h 41m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2339,20 +2339,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Manoj Karanjit</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841348904</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841348904</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2387,10 +2381,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.68287</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.68287</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2446,25 +2438,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.3856</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.3856</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -2513,7 +2501,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3340,7 +3328,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2481,6 +2481,217 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380358</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Yashu Karki</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Yashu Karki</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841840682</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:22:39 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841840682</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:35:28 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:22:39 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.73707</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Maharajung, Kanti Sangam Marg, Next to Holy Bell Girls Hostel Maharajgunj, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>blitzshreya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>08:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.32845</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>22h 47m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2492,7 +2703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2501,7 +2712,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2529,7 +2740,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2539,7 +2750,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2550,7 +2761,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2785,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 17h 9m</t>
+          <t>1d 14h 51m</t>
         </is>
       </c>
     </row>
@@ -2615,10 +2826,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2723,10 +2934,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3362,6 +3573,73 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380358</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Yashu Karki</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:22:39 PM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:35:28 PM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:22:39 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>22h 47m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2548,10 +2548,8 @@
           <t>Yashu Karki</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841840682</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841840682</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2586,10 +2584,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.73707</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.73707</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -2645,25 +2641,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L36-3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.32845</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.32845</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2712,7 +2704,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3606,7 +3598,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW11"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2684,6 +2684,217 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379202</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Paudel</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Paudel</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9840056783</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9840056783</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:53:02 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.7322</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Sukedhara , Nilo Pul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>nabin78paudel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>19:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L6-6</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.35031</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2695,7 +2906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2704,7 +2915,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2732,7 +2943,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2742,7 +2953,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -2753,7 +2964,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2988,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 14h 51m</t>
+          <t>1d 15h 52m</t>
         </is>
       </c>
     </row>
@@ -2818,10 +3029,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -2926,10 +3137,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3632,6 +3843,73 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1379202</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Nabin Paudel</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:53:02 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>1d 23h 56m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2751,10 +2751,8 @@
           <t>Nabin Paudel</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9840056783</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9840056783</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2789,10 +2787,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.7322</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.7322</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2848,50 +2844,257 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L6-6</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.35031</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.35030999999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 2:10 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Call back</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1274645</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Sakar Giri</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Sakar Giri</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9841864340</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9841864340</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>26 Jul 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73427</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Budhanilkantha Kapan ward no:11 kharibot near Kapan,kharibot ani gumba, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>sakargiri99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>12:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L35-1</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.35373</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 56m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>93d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2906,7 +3109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2943,7 +3146,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2953,7 +3156,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2964,7 +3167,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -2988,7 +3191,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 15h 52m</t>
+          <t>10d 21h 25m</t>
         </is>
       </c>
     </row>
@@ -3029,10 +3232,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -3137,10 +3340,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -3876,14 +4079,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 01:49:26 PM</t>
@@ -3907,6 +4110,73 @@
       <c r="M33" s="5" t="inlineStr">
         <is>
           <t>1d 23h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1274645</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Sakar Giri</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>26 Jul 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>93d 23h 21m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2954,10 +2954,8 @@
           <t>Sakar Giri</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9841864340</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9841864340</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -2992,10 +2990,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73427</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73427</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3051,25 +3047,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L35-1</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.35373</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.35373</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Call back  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3118,7 +3110,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4146,7 +4138,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : Call back  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3090,6 +3090,213 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV buffering issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380264</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Nirmala Gurung</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Nirmala Gurung</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9818606881</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:52:31 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9818606881</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:24 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:52:31 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.744901</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Duda nilakanth, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>11:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.36259</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3101,7 +3308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3110,7 +3317,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3138,7 +3345,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -3148,7 +3355,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -3159,7 +3366,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -3183,7 +3390,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>10d 21h 25m</t>
+          <t>9d 23h 58m</t>
         </is>
       </c>
     </row>
@@ -3260,10 +3467,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -3397,7 +3604,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3413,181 +3620,137 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
       <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1379169</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Pragal Kc</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>IPTV STB Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 01:29:57 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1380004</t>
+          <t>TKT1379169</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Chhechima Sherpa</t>
+          <t>Pragal Kc</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -3607,22 +3770,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 10:33:24 AM</t>
+          <t>26 Oct 2026 01:29:57 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -3632,19 +3795,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 2m</t>
+          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1379167</t>
+          <t>TKT1380004</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Kamal Pandit</t>
+          <t>Chhechima Sherpa</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3674,22 +3837,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:27:43 PM</t>
+          <t>27 Oct 2026 10:33:24 AM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3699,19 +3862,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 39m</t>
+          <t>1d 2m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1379187</t>
+          <t>TKT1379167</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Dhijan Dahal</t>
+          <t>Kamal Pandit</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3741,22 +3904,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wfi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:24 AM</t>
+          <t>28 Oct 2026 11:06:53 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:44:30 PM</t>
+          <t>26 Oct 2026 01:27:43 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:24 AM</t>
+          <t>28 Oct 2026 11:06:53 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3766,29 +3929,29 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 21m</t>
+          <t>1d 21h 39m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1379325</t>
+          <t>TKT1379187</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sanu Maya Tamang</t>
+          <t>Dhijan Dahal</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3808,22 +3971,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:43:41 AM</t>
+          <t>28 Oct 2026 11:06:24 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:42:44 PM</t>
+          <t>26 Oct 2026 01:44:30 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:43:41 AM</t>
+          <t>28 Oct 2026 11:06:24 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3833,29 +3996,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 20h</t>
+          <t>1d 21h 21m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1379645</t>
+          <t>TKT1379325</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>delight outsource security serves pvt</t>
+          <t>Sanu Maya Tamang</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3875,22 +4038,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:18:27 PM</t>
+          <t>28 Oct 2026 11:43:41 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 07:31:56 PM</t>
+          <t>26 Oct 2026 03:42:44 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:18:27 PM</t>
+          <t>28 Oct 2026 11:43:41 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3900,29 +4063,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 16h 46m</t>
+          <t>1d 20h</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1379467</t>
+          <t>TKT1379645</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Manoj Karanjit</t>
+          <t>delight outsource security serves pvt</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3942,22 +4105,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:43:39 PM</t>
+          <t>28 Oct 2026 12:18:27 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 05:02:06 PM</t>
+          <t>26 Oct 2026 07:31:56 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:43:39 PM</t>
+          <t>28 Oct 2026 12:18:27 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -3967,19 +4130,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 19h 41m</t>
+          <t>1d 16h 46m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1380358</t>
+          <t>TKT1379467</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Yashu Karki</t>
+          <t>Manoj Karanjit</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -4009,22 +4172,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:22:39 PM</t>
+          <t>28 Oct 2026 12:43:39 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>27 Oct 2026 02:35:28 PM</t>
+          <t>26 Oct 2026 05:02:06 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:22:39 PM</t>
+          <t>28 Oct 2026 12:43:39 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4034,19 +4197,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>22h 47m</t>
+          <t>1d 19h 41m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1379202</t>
+          <t>TKT1380358</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Nabin Paudel</t>
+          <t>Yashu Karki</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4081,17 +4244,17 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:49:26 PM</t>
+          <t>28 Oct 2026 01:22:39 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:53:02 PM</t>
+          <t>27 Oct 2026 02:35:28 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:49:26 PM</t>
+          <t>28 Oct 2026 01:22:39 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -4101,74 +4264,208 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>1d 23h 56m</t>
+          <t>22h 47m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>TKT1379202</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Paudel</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:53:02 PM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 56m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>TKT1274645</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Sakar Giri</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Case : Call back  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 02:10:10 PM</t>
         </is>
       </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>26 Jul 2026 02:49:04 PM</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 02:10:10 PM</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M34" s="3" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>93d 23h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380264</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Nirmala Gurung</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:52:31 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:24 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:52:31 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3157,10 +3157,8 @@
           <t>Nirmala Gurung</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9818606881</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9818606881</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3195,10 +3193,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.744901</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.744901</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3250,25 +3246,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L27-7</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.36259</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.36259</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3317,7 +3309,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4435,7 +4427,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -510,14 +510,14 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -527,9 +527,9 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3289,6 +3289,1658 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:16 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381041</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Digam Kumar Rana</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Digam Kumar Rana</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9702683606</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:16:18 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9810214387</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:17:30 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:16:18 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.6553579</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Buddha Party Palace,Tikathali, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>zarusmagar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>06:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.3559794</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:09 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380806</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.67349</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, ghatthaghar near by nepal telecom, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>aayushsth77@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L51-6</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.37342</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>20h 1m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>20h 1m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:07 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381003</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Riwaz Thapa</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Riwaz Thapa</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9843819136</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 09:44:42 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>BKT9843819136</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 09:44:42 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:07:28 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Marigold E.B. School - School merigold english boarding school balkot,bhaktapur,near 32701, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>9841479321@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L21-6</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:06 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380906</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Khadka</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Khadka</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9813192017</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:02:33 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9813286073</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:02:33 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:06:46 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.667993</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Balkot, Brihaspati Marg -2, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>khadkaanjuli1998@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.368072</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>9h 4m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>9h 4m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:06 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379390</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Ulak</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Ulak</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9861691382</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:27:35 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9861691382</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:27:35 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:06:03 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.6781</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>61 koteshwor sky bridge, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>prashant9843215397@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.34772</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:04 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380633</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Anurag Karki</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Anurag Karki</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861095557</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:56 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861095557</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 06:12:47 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:56 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Public Health Office Bhaktapur - Government office MC74+4PG Unnamed Road Suryabinayak 44800  , Bhakt</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>anuragkarki6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>08:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>22h 52m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:04 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379373</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar Regmi</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar Regmi</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9811566677</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:01 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9811566677</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:20:05 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:01 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.69851</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Basuki Marga, Ghumnti Kumari Marga, Near To Rabindra Cold Store &amp; Nepal investment and Securities Tr</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>regmi48ramesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>20:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L57-3</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.34308</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 43m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:03 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380397</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Ale</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Ale</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9803609995</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:03:09 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9803609995</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:07:09 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:03:09 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.66715</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Ekantakuna lalitpur near Tibetan Laphing Center, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.30986</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 56m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3300,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3309,7 +4961,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3337,7 +4989,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -3347,7 +4999,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3358,7 +5010,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -3382,7 +5034,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>9d 23h 58m</t>
+          <t>7d 14h 56m</t>
         </is>
       </c>
     </row>
@@ -3423,14 +5075,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -3531,37 +5183,37 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -3573,30 +5225,30 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -3619,7 +5271,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -3635,181 +5287,137 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
-      <c r="B22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
       <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1379169</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>Pragal Kc</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>IPTV STB Adaptor damage Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>26 Oct 2026 01:29:57 PM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>28 Oct 2026 10:05:05 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 20h 35m</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1380004</t>
+          <t>TKT1379169</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Chhechima Sherpa</t>
+          <t>Pragal Kc</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -3829,22 +5437,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>27 Oct 2026 10:33:24 AM</t>
+          <t>26 Oct 2026 01:29:57 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 10:36:01 AM</t>
+          <t>28 Oct 2026 10:05:05 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -3854,19 +5462,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 2m</t>
+          <t>1d 20h 35m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1379167</t>
+          <t>TKT1380004</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Kamal Pandit</t>
+          <t>Chhechima Sherpa</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3896,22 +5504,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:27:43 PM</t>
+          <t>27 Oct 2026 10:33:24 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:53 AM</t>
+          <t>28 Oct 2026 10:36:01 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3921,19 +5529,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 21h 39m</t>
+          <t>1d 2m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1379187</t>
+          <t>TKT1379167</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Dhijan Dahal</t>
+          <t>Kamal Pandit</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3963,22 +5571,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wfi6  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:24 AM</t>
+          <t>28 Oct 2026 11:06:53 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:44:30 PM</t>
+          <t>26 Oct 2026 01:27:43 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:06:24 AM</t>
+          <t>28 Oct 2026 11:06:53 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3988,29 +5596,29 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 21h 21m</t>
+          <t>1d 21h 39m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1379325</t>
+          <t>TKT1379187</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Sanu Maya Tamang</t>
+          <t>Dhijan Dahal</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -4030,22 +5638,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:43:41 AM</t>
+          <t>28 Oct 2026 11:06:24 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 03:42:44 PM</t>
+          <t>26 Oct 2026 01:44:30 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 11:43:41 AM</t>
+          <t>28 Oct 2026 11:06:24 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4055,29 +5663,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 20h</t>
+          <t>1d 21h 21m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1379645</t>
+          <t>TKT1379325</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>delight outsource security serves pvt</t>
+          <t>Sanu Maya Tamang</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -4097,22 +5705,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:18:27 PM</t>
+          <t>28 Oct 2026 11:43:41 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>26 Oct 2026 07:31:56 PM</t>
+          <t>26 Oct 2026 03:42:44 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:18:27 PM</t>
+          <t>28 Oct 2026 11:43:41 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -4122,29 +5730,29 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>1d 16h 46m</t>
+          <t>1d 20h</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1379467</t>
+          <t>TKT1379645</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Manoj Karanjit</t>
+          <t>delight outsource security serves pvt</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -4164,22 +5772,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:43:39 PM</t>
+          <t>28 Oct 2026 12:18:27 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 05:02:06 PM</t>
+          <t>26 Oct 2026 07:31:56 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 12:43:39 PM</t>
+          <t>28 Oct 2026 12:18:27 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4189,19 +5797,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1d 19h 41m</t>
+          <t>1d 16h 46m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1380358</t>
+          <t>TKT1379467</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Yashu Karki</t>
+          <t>Manoj Karanjit</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -4231,22 +5839,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:22:39 PM</t>
+          <t>28 Oct 2026 12:43:39 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>27 Oct 2026 02:35:28 PM</t>
+          <t>26 Oct 2026 05:02:06 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:22:39 PM</t>
+          <t>28 Oct 2026 12:43:39 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -4256,19 +5864,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>22h 47m</t>
+          <t>1d 19h 41m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1379202</t>
+          <t>TKT1380358</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Nabin Paudel</t>
+          <t>Yashu Karki</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -4303,17 +5911,17 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:49:26 PM</t>
+          <t>28 Oct 2026 01:22:39 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>26 Oct 2026 01:53:02 PM</t>
+          <t>27 Oct 2026 02:35:28 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>28 Oct 2026 01:49:26 PM</t>
+          <t>28 Oct 2026 01:22:39 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4323,19 +5931,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 23h 56m</t>
+          <t>22h 47m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1274645</t>
+          <t>TKT1379202</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Sakar Giri</t>
+          <t>Nabin Paudel</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -4365,22 +5973,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : Call back  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:10:10 PM</t>
+          <t>28 Oct 2026 01:49:26 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>26 Jul 2026 02:49:04 PM</t>
+          <t>26 Oct 2026 01:53:02 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>28 Oct 2026 02:10:10 PM</t>
+          <t>28 Oct 2026 01:49:26 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -4390,74 +5998,409 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>93d 23h 21m</t>
+          <t>1d 23h 56m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>TKT1274645</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Sakar Giri</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>26 Jul 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>93d 23h 21m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>TKT1380264</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Nirmala Gurung</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="I36" s="3" t="inlineStr">
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 02:52:31 PM</t>
         </is>
       </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>27 Oct 2026 01:25:24 PM</t>
         </is>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>28 Oct 2026 02:52:31 PM</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M36" s="3" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>1d 1h 27m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381041</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Digam Kumar Rana</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:16:18 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:17:30 AM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:16:18 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380633</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Anurag Karki</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:56 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 06:12:47 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:56 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>22h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379373</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar Regmi</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:01 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:20:05 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:01 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>2d 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1380397</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Sunil Ale</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:03:09 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:07:09 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:03:09 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 56m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_28_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_28_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3356,10 +3356,8 @@
           <t>Digam Kumar Rana</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9702683606</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9702683606</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3394,10 +3392,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.6553579</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.6553579</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3453,25 +3449,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.3559794</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.3559794</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -3567,10 +3559,8 @@
           <t>Aayush shrestha</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9843468465</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9843468465</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3605,10 +3595,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.67349</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.67349</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -3660,25 +3648,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L51-6</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.37342</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.37342</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3774,10 +3758,8 @@
           <t>Riwaz Thapa</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9843819136</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9843819136</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3863,10 +3845,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3877,7 +3857,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -3973,10 +3953,8 @@
           <t>Anjali Khadka</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9813192017</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9813192017</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4011,10 +3989,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.667993</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.667993</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4066,25 +4042,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.368072</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.368072</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4180,10 +4152,8 @@
           <t>Prashant Ulak</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9861691382</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9861691382</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4218,10 +4188,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.6781</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.6781</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4273,25 +4241,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.34772</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.34772</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4387,10 +4351,8 @@
           <t>Anurag Karki</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861095557</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861095557</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4480,10 +4442,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4494,7 +4454,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4590,10 +4550,8 @@
           <t>Ramesh Kumar Regmi</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9811566677</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9811566677</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4628,10 +4586,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.69851</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.69851</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -4687,25 +4643,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>L57-3</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.34308</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.34308</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4801,10 +4753,8 @@
           <t>Sunil Ale</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9803609995</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9803609995</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4839,10 +4789,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.66715</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.66715</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -4894,25 +4842,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.30986</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30986</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4961,7 +4905,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6169,7 +6113,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
@@ -6236,7 +6180,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -6303,7 +6247,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6370,7 +6314,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
